--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980" firstSheet="2" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,11 @@
     <sheet name="Conferences" sheetId="6" r:id="rId6"/>
     <sheet name="Publications" sheetId="7" r:id="rId7"/>
     <sheet name="WorkingPapers" sheetId="8" r:id="rId8"/>
+    <sheet name="UnderwayResearch" sheetId="10" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="186">
   <si>
     <t>Dates</t>
   </si>
@@ -343,51 +347,27 @@
     <t>Coauthors</t>
   </si>
   <si>
-    <t>The Nonlinear _x000D_
-                                   Effects of Pollution on Crime: Evidence from Mexico City and New York</t>
-  </si>
-  <si>
     <t>Environmental Research - Health</t>
   </si>
   <si>
-    <t>Air Pollution _x000D_
-                                   and the Productivity of High-Skill Labor: Evidence from Court Hearings</t>
-  </si>
-  <si>
     <t>Scandinavian Journal of Economics 124: 301-332.</t>
   </si>
   <si>
-    <t>Mexico and US _x000D_
-                              Power Systems Under Variations in Natural Gas Prices</t>
-  </si>
-  <si>
     <t>Energy Policy, 151, 113378</t>
   </si>
   <si>
     <t>Juan Rosellon, Sauleh Sidiqui, Max Brown, Avraam Charalampos, Anahi Molar, Baltazar Solano</t>
   </si>
   <si>
-    <t>The Role of Energy_x000D_
-                              Storage in the Uptake of Renewable Energy: A Model Comparison Approach</t>
-  </si>
-  <si>
     <t>Energy Policy 151, 112159</t>
   </si>
   <si>
     <t>Sara Giarola, Kathleen Vaillancourt, Max Brown, Anahi Molar, Ivan Garcia Kerdan</t>
   </si>
   <si>
-    <t>The Effects of _x000D_
-                                   the 2013 Floods on Germany's Road Freight Traffic</t>
-  </si>
-  <si>
     <t>Julio Fournier</t>
   </si>
   <si>
-    <t>Analysing Scenarios for the Integration of _x000D_
-                                   Renewable Energy Sources in the Mexican Energy System</t>
-  </si>
-  <si>
     <t>Energies, 12.17, 3270</t>
   </si>
   <si>
@@ -458,16 +438,180 @@
   </si>
   <si>
     <t>Scientific support to institutional activities. Mentoring of junior scholars. Applied econometrics and _x000D_ the development of agent-based models. Study the relationship between transport, digitalization, and the environment as part of the EU 2D4D project.</t>
+  </si>
+  <si>
+    <t>link</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.eiee.org/'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.diw.de/en'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.hertie-school.org/en/'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.bb.com.mx/webcenter/portal/BanBajio/home?_afrRedirect=64903577593997558'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.tu.berlin/en/'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.hu-berlin.de/en'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://bajio.delasalle.edu.mx/'&gt;</t>
+  </si>
+  <si>
+    <t>The Nonlinear _x000D_ Effects of Pollution on Crime: Evidence from Mexico City and New York</t>
+  </si>
+  <si>
+    <t>The Role of Energy_x000D_ Storage in the Uptake of Renewable Energy: A Model Comparison Approach</t>
+  </si>
+  <si>
+    <t>Mexico and US Power Systems Under Variations in Natural Gas Prices</t>
+  </si>
+  <si>
+    <t>Analysing Scenarios for the Integration of _x000D_ Renewable Energy Sources in the Mexican Energy System</t>
+  </si>
+  <si>
+    <t>The Effects of _x000D_the 2013 Floods on Germany's Road Freight Traffic</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://doi.org/10.1088/2752-5309/ac9a65'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://onlinelibrary.wiley.com/doi/full/10.1111/sjoe.12458'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.sciencedirect.com/science/article/abs/pii/S0301421521002482'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.sciencedirect.com/science/article/abs/pii/S0301421521000288'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href = 'https://www.sciencedirect.com/science/article/abs/pii/S1361920919307278'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href= 'https://www.mdpi.com/1996-1073/12/17/3270'&gt;</t>
+  </si>
+  <si>
+    <t>Institute</t>
+  </si>
+  <si>
+    <t>RFF-CMCC: European Institute on Economics and the Environment</t>
+  </si>
+  <si>
+    <t>RFF-CMCC: European Institute on Economics and the Environment and DIW Berlin</t>
+  </si>
+  <si>
+    <t>German Institute of Economic Research (DIW Berlin)</t>
+  </si>
+  <si>
+    <t>Institutes</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment and KID School of Public Policy</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment and Bocconi University</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment, German_x000D_ Institute of Economic Research, and Leibniz Institute for Economic Research</t>
+  </si>
+  <si>
+    <t>econometrics</t>
+  </si>
+  <si>
+    <t>modeling</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Expected</t>
+  </si>
+  <si>
+    <t>Winter 2022</t>
+  </si>
+  <si>
+    <t>Spring 2023</t>
+  </si>
+  <si>
+    <t>Air Quality and School Abenteeism: Evidence from New York City</t>
+  </si>
+  <si>
+    <t>Spring 2022</t>
+  </si>
+  <si>
+    <t>Air Pollution and Domestic Violence</t>
+  </si>
+  <si>
+    <t>Ireri Hernandez</t>
+  </si>
+  <si>
+    <t>The Effect of Changing Marginal Cost to Physical Order Dispatch in the Power Sector</t>
+  </si>
+  <si>
+    <t>Raul Gutierrez and Juan Rosellón</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment, University of Chicago, and CIDE Mexico</t>
+  </si>
+  <si>
+    <t>WorkingVersion</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Fall 2023</t>
+  </si>
+  <si>
+    <t>U.S. Net-Zero Technology Pathways of Carbon Management</t>
+  </si>
+  <si>
+    <t>John Bistline, Carol Lenox, Nadja Victor, Gokul Iyer, Mathew Binsted, Leonard Göke, and others</t>
+  </si>
+  <si>
+    <t>Studying EMF37 high-electrification scenarios in the European Context.</t>
+  </si>
+  <si>
+    <t>Johannes Emmerling, Leonard Göke, Karlo Hainsch</t>
+  </si>
+  <si>
+    <t>European Institute on Economics and the Environment, TU Berlin</t>
+  </si>
+  <si>
+    <t>European Instiute on Economics and the Environment, TU Berlin, USDAM ONNL, UMD, NETL, EPA, MIT, NREL</t>
+  </si>
+  <si>
+    <t>Underlying assumptions across the Atlantic Looking at heterogenous assumptions in North American and European energy models</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -490,10 +634,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -504,8 +649,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -784,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.140625" style="2" customWidth="1"/>
@@ -792,10 +942,11 @@
     <col min="3" max="3" width="47.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.7109375" style="2" customWidth="1"/>
     <col min="5" max="5" width="63.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="2"/>
+    <col min="6" max="6" width="31.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -811,8 +962,11 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="F1" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -826,10 +980,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -843,10 +1000,13 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -860,10 +1020,13 @@
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
@@ -879,8 +1042,11 @@
       <c r="E5" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>18</v>
       </c>
@@ -895,6 +1061,9 @@
       </c>
       <c r="E6" s="2" t="s">
         <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -905,16 +1074,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -930,8 +1101,11 @@
       <c r="E1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -947,8 +1121,11 @@
       <c r="E2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -964,8 +1141,11 @@
       <c r="E3" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -980,6 +1160,9 @@
       </c>
       <c r="E4" t="s">
         <v>36</v>
+      </c>
+      <c r="F4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -1208,7 +1391,7 @@
       <c r="C2" t="s">
         <v>62</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E2">
@@ -1225,7 +1408,7 @@
       <c r="C3" t="s">
         <v>65</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E3">
@@ -1242,7 +1425,7 @@
       <c r="C4" t="s">
         <v>67</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E4">
@@ -1259,7 +1442,7 @@
       <c r="C5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E5">
@@ -1276,7 +1459,7 @@
       <c r="C6" t="s">
         <v>67</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E6">
@@ -1293,7 +1476,7 @@
       <c r="C7" t="s">
         <v>74</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E7">
@@ -1310,7 +1493,7 @@
       <c r="C8" t="s">
         <v>77</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="5" t="s">
         <v>78</v>
       </c>
       <c r="E8">
@@ -1327,7 +1510,7 @@
       <c r="C9" t="s">
         <v>81</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="5" t="s">
         <v>82</v>
       </c>
       <c r="E9">
@@ -1344,7 +1527,7 @@
       <c r="C10" t="s">
         <v>85</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="5" t="s">
         <v>86</v>
       </c>
       <c r="E10">
@@ -1361,7 +1544,7 @@
       <c r="C11" t="s">
         <v>88</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="5" t="s">
         <v>89</v>
       </c>
       <c r="E11">
@@ -1378,7 +1561,7 @@
       <c r="C12" t="s">
         <v>91</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E12">
@@ -1395,7 +1578,7 @@
       <c r="C13" t="s">
         <v>65</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="5" t="s">
         <v>14</v>
       </c>
       <c r="E13">
@@ -1412,7 +1595,7 @@
       <c r="C14" t="s">
         <v>94</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="5" t="s">
         <v>95</v>
       </c>
       <c r="E14">
@@ -1420,16 +1603,40 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1"/>
+    <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="D4" r:id="rId3"/>
+    <hyperlink ref="D5" r:id="rId4"/>
+    <hyperlink ref="D6" r:id="rId5"/>
+    <hyperlink ref="D7" r:id="rId6"/>
+    <hyperlink ref="D8" r:id="rId7"/>
+    <hyperlink ref="D9" r:id="rId8"/>
+    <hyperlink ref="D10" r:id="rId9"/>
+    <hyperlink ref="D11" r:id="rId10"/>
+    <hyperlink ref="D12" r:id="rId11"/>
+    <hyperlink ref="D13" r:id="rId12"/>
+    <hyperlink ref="D14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="43.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5703125" customWidth="1"/>
+    <col min="5" max="5" width="27.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="51.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>99</v>
       </c>
@@ -1442,206 +1649,595 @@
       <c r="D1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" t="s">
         <v>103</v>
       </c>
-      <c r="C2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2021</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2021</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="C7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>111</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G6" r:id="rId1"/>
+    <hyperlink ref="G7" r:id="rId2"/>
+    <hyperlink ref="G5" r:id="rId3"/>
+    <hyperlink ref="G4" r:id="rId4"/>
+    <hyperlink ref="G3" r:id="rId5"/>
+    <hyperlink ref="G2" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="48.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>100</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2019</v>
       </c>
-      <c r="B3" t="s">
-        <v>124</v>
+      <c r="B3" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="C3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2018</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
-      <c r="B5" t="s">
-        <v>130</v>
+      <c r="B5" s="1" t="s">
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2022</v>
       </c>
-      <c r="B6" t="s">
-        <v>133</v>
+      <c r="B6" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2020</v>
       </c>
-      <c r="B7" t="s">
-        <v>135</v>
+      <c r="B7" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" t="s">
-        <v>136</v>
+        <v>125</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>2022</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2022</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2022</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2022</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9">
+    <sortState ref="A2:F6">
+      <sortCondition descending="1" ref="A1:A6"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980" firstSheet="2" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="185">
   <si>
     <t>Dates</t>
   </si>
@@ -191,9 +191,6 @@
     <t>Quarto</t>
   </si>
   <si>
-    <t>Markdown</t>
-  </si>
-  <si>
     <t>Git</t>
   </si>
   <si>
@@ -593,7 +590,7 @@
     <t>European Instiute on Economics and the Environment, TU Berlin, USDAM ONNL, UMD, NETL, EPA, MIT, NREL</t>
   </si>
   <si>
-    <t>Underlying assumptions across the Atlantic Looking at heterogenous assumptions in North American and European energy models</t>
+    <t>Underlying Beliefs across the Atlantic Looking at heterogenous assumptions in North American and European energy models</t>
   </si>
 </sst>
 </file>
@@ -963,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -980,10 +977,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1000,10 +997,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1020,10 +1017,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1043,7 +1040,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1063,7 +1060,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1102,7 +1099,7 @@
         <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1122,7 +1119,7 @@
         <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1142,7 +1139,7 @@
         <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1162,7 +1159,7 @@
         <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1223,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -1270,7 +1267,7 @@
         <v>52</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1278,7 +1275,7 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -1286,14 +1283,6 @@
         <v>54</v>
       </c>
       <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8">
         <v>2</v>
       </c>
     </row>
@@ -1317,7 +1306,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1325,7 +1314,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -1333,7 +1322,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -1341,7 +1330,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -1366,30 +1355,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
         <v>96</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>97</v>
-      </c>
-      <c r="C1" t="s">
-        <v>98</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" t="s">
         <v>60</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" t="s">
-        <v>62</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
@@ -1400,13 +1389,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>14</v>
@@ -1417,13 +1406,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" t="s">
         <v>66</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" t="s">
-        <v>67</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>14</v>
@@ -1434,13 +1423,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
         <v>68</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>70</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
@@ -1451,13 +1440,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>14</v>
@@ -1468,13 +1457,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
@@ -1485,16 +1474,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s">
         <v>75</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>76</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="E8">
         <v>2019</v>
@@ -1502,16 +1491,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" t="s">
         <v>79</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>80</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="E9">
         <v>2019</v>
@@ -1519,16 +1508,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
         <v>83</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>84</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>86</v>
       </c>
       <c r="E10">
         <v>2018</v>
@@ -1536,16 +1525,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
         <v>87</v>
       </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="E11">
         <v>2018</v>
@@ -1553,13 +1542,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
         <v>90</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>91</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>14</v>
@@ -1570,13 +1559,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>14</v>
@@ -1587,16 +1576,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
         <v>93</v>
       </c>
-      <c r="B14" t="s">
-        <v>84</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" s="5" t="s">
         <v>94</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>95</v>
       </c>
       <c r="E14">
         <v>2017</v>
@@ -1638,28 +1627,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
         <v>99</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>101</v>
       </c>
-      <c r="D1" t="s">
-        <v>102</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1667,22 +1656,22 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1690,22 +1679,22 @@
         <v>2021</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1713,25 +1702,25 @@
         <v>2021</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
         <v>105</v>
       </c>
-      <c r="D4" t="s">
-        <v>106</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1739,25 +1728,25 @@
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1765,25 +1754,25 @@
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1791,25 +1780,25 @@
         <v>2019</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" t="s">
         <v>110</v>
       </c>
-      <c r="D7" t="s">
-        <v>111</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1840,28 +1829,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
         <v>100</v>
       </c>
-      <c r="C1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>102</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1869,25 +1858,25 @@
         <v>2021</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D2" t="s">
         <v>115</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1895,25 +1884,25 @@
         <v>2019</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3" t="s">
         <v>118</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>119</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="F3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G3" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="H3" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1921,25 +1910,25 @@
         <v>2018</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="F4" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1947,22 +1936,22 @@
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
         <v>124</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>126</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="H5" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1970,22 +1959,22 @@
         <v>2022</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C6" t="s">
-        <v>125</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1993,22 +1982,22 @@
         <v>2020</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2016,22 +2005,22 @@
         <v>2021</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2057,22 +2046,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2080,19 +2069,19 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2100,19 +2089,19 @@
         <v>2022</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C3" t="s">
-        <v>167</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2120,19 +2109,19 @@
         <v>2022</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2140,19 +2129,19 @@
         <v>2022</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="C5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2160,19 +2149,19 @@
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" t="s">
         <v>161</v>
-      </c>
-      <c r="F6" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2180,19 +2169,19 @@
         <v>2021</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C7" t="s">
-        <v>167</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2200,16 +2189,16 @@
         <v>2020</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" t="s">
         <v>168</v>
       </c>
-      <c r="C8" t="s">
-        <v>169</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F8" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2217,19 +2206,19 @@
         <v>2020</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C9" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21435" windowHeight="10980" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -122,9 +122,6 @@
     <t>Berlin Institute of Technology</t>
   </si>
   <si>
-    <t>An Econometric Analysis of Envvironmental Phenomena</t>
-  </si>
-  <si>
     <t>Sep.2014 Apr.2016</t>
   </si>
   <si>
@@ -434,9 +431,6 @@
     <t>Research and publication of scientific articles in the realm of energy and environmental economics. _x000D_Research projects on the effects of air pollution and air pollution control policies on productivity, _x000D_health, and wellbeing.</t>
   </si>
   <si>
-    <t>Scientific support to institutional activities. Mentoring of junior scholars. Applied econometrics and _x000D_ the development of agent-based models. Study the relationship between transport, digitalization, and the environment as part of the EU 2D4D project.</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
@@ -591,6 +585,13 @@
   </si>
   <si>
     <t>Underlying Beliefs across the Atlantic Looking at heterogenous assumptions in North American and European energy models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scientific support to institutional activities. Mentoring of junior scholars. Applied econometrics and the development of agent-based models. Study the relationship between transport, digitalization, and the environment as part of the EU 2D4D project.   
+ </t>
+  </si>
+  <si>
+    <t>An Econometric Analysis of Environmental Phenomena</t>
   </si>
 </sst>
 </file>
@@ -960,10 +961,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -977,10 +978,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -997,10 +998,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1017,10 +1018,10 @@
         <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,7 +1041,7 @@
         <v>17</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1060,7 +1061,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1099,7 +1100,7 @@
         <v>24</v>
       </c>
       <c r="F1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -1116,50 +1117,50 @@
         <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="F2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>30</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1178,42 +1179,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
         <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
         <v>40</v>
-      </c>
-      <c r="B3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
         <v>42</v>
-      </c>
-      <c r="B4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
-      </c>
-      <c r="B5" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1232,15 +1233,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1248,7 +1249,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -1256,7 +1257,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4">
         <v>5</v>
@@ -1264,7 +1265,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -1272,7 +1273,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6">
         <v>3</v>
@@ -1280,7 +1281,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -1298,15 +1299,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
         <v>47</v>
-      </c>
-      <c r="B1" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2">
         <v>5</v>
@@ -1314,7 +1315,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B3">
         <v>5</v>
@@ -1322,7 +1323,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -1330,7 +1331,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -1355,30 +1356,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" t="s">
         <v>95</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>96</v>
-      </c>
-      <c r="C1" t="s">
-        <v>97</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>60</v>
-      </c>
-      <c r="C2" t="s">
-        <v>61</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
@@ -1389,13 +1390,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s">
         <v>62</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>63</v>
-      </c>
-      <c r="C3" t="s">
-        <v>64</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>14</v>
@@ -1406,13 +1407,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
         <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" t="s">
-        <v>66</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>14</v>
@@ -1423,13 +1424,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B5" t="s">
         <v>67</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>69</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>8</v>
@@ -1440,13 +1441,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>14</v>
@@ -1457,13 +1458,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
         <v>71</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>73</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>14</v>
@@ -1474,16 +1475,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>75</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="E8">
         <v>2019</v>
@@ -1491,16 +1492,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" t="s">
         <v>78</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>79</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="5" t="s">
         <v>80</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>81</v>
       </c>
       <c r="E9">
         <v>2019</v>
@@ -1508,16 +1509,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>81</v>
+      </c>
+      <c r="B10" t="s">
         <v>82</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>83</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="5" t="s">
         <v>84</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>85</v>
       </c>
       <c r="E10">
         <v>2018</v>
@@ -1525,16 +1526,16 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11" t="s">
         <v>86</v>
       </c>
-      <c r="B11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="D11" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="E11">
         <v>2018</v>
@@ -1542,13 +1543,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>88</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
         <v>89</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>14</v>
@@ -1559,13 +1560,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>14</v>
@@ -1576,16 +1577,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
         <v>92</v>
       </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>94</v>
       </c>
       <c r="E14">
         <v>2017</v>
@@ -1627,28 +1628,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" t="s">
         <v>98</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" t="s">
-        <v>101</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1656,22 +1657,22 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1679,22 +1680,22 @@
         <v>2021</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1702,25 +1703,25 @@
         <v>2021</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
         <v>104</v>
       </c>
-      <c r="D4" t="s">
-        <v>105</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1728,25 +1729,25 @@
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" t="s">
         <v>106</v>
       </c>
-      <c r="D5" t="s">
-        <v>107</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>8</v>
       </c>
       <c r="H5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1754,25 +1755,25 @@
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1780,25 +1781,25 @@
         <v>2019</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D7" t="s">
         <v>109</v>
       </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -1829,28 +1830,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C1" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" t="s">
         <v>99</v>
       </c>
-      <c r="C1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -1858,25 +1859,25 @@
         <v>2021</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D2" t="s">
         <v>114</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1884,25 +1885,25 @@
         <v>2019</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" t="s">
         <v>117</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>118</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1910,25 +1911,25 @@
         <v>2018</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -1936,22 +1937,22 @@
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" t="s">
         <v>123</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1959,22 +1960,22 @@
         <v>2022</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -1982,22 +1983,22 @@
         <v>2020</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="45" x14ac:dyDescent="0.25">
@@ -2005,22 +2006,22 @@
         <v>2021</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C8" t="s">
-        <v>124</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2046,22 +2047,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2069,19 +2070,19 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2089,19 +2090,19 @@
         <v>2022</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="C3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>182</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="45" x14ac:dyDescent="0.25">
@@ -2109,19 +2110,19 @@
         <v>2022</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2129,19 +2130,19 @@
         <v>2022</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -2149,19 +2150,19 @@
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2169,19 +2170,19 @@
         <v>2021</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2189,16 +2190,16 @@
         <v>2020</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C8" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" t="s">
         <v>159</v>
-      </c>
-      <c r="F8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -2206,19 +2207,19 @@
         <v>2020</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,25 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luissarmiento/Dropbox (CMCC)/EIEE/Website/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064E329E-6D69-4A45-9BC9-22BED21A8F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A406FA-89BA-8945-B650-DAC3F1F814CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="19200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
     <sheet name="Education" sheetId="2" r:id="rId2"/>
-    <sheet name="Research Interests" sheetId="3" r:id="rId3"/>
-    <sheet name="Software" sheetId="4" r:id="rId4"/>
-    <sheet name="Languages" sheetId="5" r:id="rId5"/>
-    <sheet name="Conferences" sheetId="6" r:id="rId6"/>
-    <sheet name="Teaching" sheetId="11" r:id="rId7"/>
-    <sheet name="Publications" sheetId="7" r:id="rId8"/>
-    <sheet name="WorkingPapers" sheetId="8" r:id="rId9"/>
-    <sheet name="UnderwayResearch" sheetId="10" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId3"/>
+    <sheet name="Research Interests" sheetId="3" r:id="rId4"/>
+    <sheet name="Software" sheetId="4" r:id="rId5"/>
+    <sheet name="Languages" sheetId="5" r:id="rId6"/>
+    <sheet name="Conferences" sheetId="6" r:id="rId7"/>
+    <sheet name="Teaching" sheetId="11" r:id="rId8"/>
+    <sheet name="Publications" sheetId="7" r:id="rId9"/>
+    <sheet name="WorkingPapers" sheetId="8" r:id="rId10"/>
+    <sheet name="UnderwayResearch" sheetId="10" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Teaching!$A$1:$A$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Teaching!$A$1:$A$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1121,6 +1122,224 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="48.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2018</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1418,6 +1637,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4C3DCE-9179-FF47-845E-F73719ADC20F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1471,7 +1699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1541,7 +1769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1591,7 +1819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -1879,7 +2107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D9F129-3957-8D46-A9B7-45930C043918}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2003,7 +2231,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2204,222 +2432,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="48.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2018</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
-</worksheet>
 </file>
--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1,33 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10514"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luissarmiento/Dropbox (CMCC)/EIEE/Website/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A406FA-89BA-8945-B650-DAC3F1F814CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E79F29-E5CF-4F4D-89E8-3E85DE70C98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="19200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
-    <sheet name="Education" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId3"/>
-    <sheet name="Research Interests" sheetId="3" r:id="rId4"/>
-    <sheet name="Software" sheetId="4" r:id="rId5"/>
-    <sheet name="Languages" sheetId="5" r:id="rId6"/>
-    <sheet name="Conferences" sheetId="6" r:id="rId7"/>
-    <sheet name="Teaching" sheetId="11" r:id="rId8"/>
-    <sheet name="Publications" sheetId="7" r:id="rId9"/>
-    <sheet name="WorkingPapers" sheetId="8" r:id="rId10"/>
-    <sheet name="UnderwayResearch" sheetId="10" r:id="rId11"/>
+    <sheet name="Publications" sheetId="7" r:id="rId2"/>
+    <sheet name="WorkingPapers" sheetId="8" r:id="rId3"/>
+    <sheet name="UnderwayResearch" sheetId="10" r:id="rId4"/>
+    <sheet name="Education" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId6"/>
+    <sheet name="Research Interests" sheetId="3" r:id="rId7"/>
+    <sheet name="Software" sheetId="4" r:id="rId8"/>
+    <sheet name="Languages" sheetId="5" r:id="rId9"/>
+    <sheet name="Conferences" sheetId="6" r:id="rId10"/>
+    <sheet name="Teaching" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Teaching!$A$1:$A$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Teaching!$A$1:$A$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="223">
   <si>
     <t>Dates</t>
   </si>
@@ -329,9 +329,6 @@
     <t>Journal</t>
   </si>
   <si>
-    <t>Coauthors</t>
-  </si>
-  <si>
     <t>Environmental Research - Health</t>
   </si>
   <si>
@@ -341,24 +338,12 @@
     <t>Energy Policy, 151, 113378</t>
   </si>
   <si>
-    <t>Juan Rosellon, Sauleh Sidiqui, Max Brown, Avraam Charalampos, Anahi Molar, Baltazar Solano</t>
-  </si>
-  <si>
     <t>Energy Policy 151, 112159</t>
   </si>
   <si>
-    <t>Sara Giarola, Kathleen Vaillancourt, Max Brown, Anahi Molar, Ivan Garcia Kerdan</t>
-  </si>
-  <si>
-    <t>Julio Fournier</t>
-  </si>
-  <si>
     <t>Energies, 12.17, 3270</t>
   </si>
   <si>
-    <t>Thorstan Burandt, Konstantin Löffler, Pao-yu Oei</t>
-  </si>
-  <si>
     <t>Transportation Research Part D, S.1022774</t>
   </si>
   <si>
@@ -371,30 +356,15 @@
     <t>Under Review</t>
   </si>
   <si>
-    <t>The Review of Economics and Statistics</t>
-  </si>
-  <si>
-    <t>Yeong-Jae Kim</t>
-  </si>
-  <si>
     <t>Effectiveness, Spillovers, and Well-Being Effects of Driving Restriction Policies</t>
   </si>
   <si>
-    <t>Revise and Resubmit</t>
-  </si>
-  <si>
     <t>Journal of Public Economics</t>
   </si>
   <si>
-    <t>Nicole Wägner and Aleksandar Zaklan</t>
-  </si>
-  <si>
     <t>Nature Sustainability</t>
   </si>
   <si>
-    <t>Julia Rechliz, Nicole Wägner, and Aleksandar Zaklan</t>
-  </si>
-  <si>
     <t>The Unaccounted Consequences of Low Emission Zones: Evidence from Madrid Central</t>
   </si>
   <si>
@@ -476,21 +446,6 @@
     <t>Institute</t>
   </si>
   <si>
-    <t>RFF-CMCC: European Institute on Economics and the Environment</t>
-  </si>
-  <si>
-    <t>RFF-CMCC: European Institute on Economics and the Environment and DIW Berlin</t>
-  </si>
-  <si>
-    <t>German Institute of Economic Research (DIW Berlin)</t>
-  </si>
-  <si>
-    <t>Institutes</t>
-  </si>
-  <si>
-    <t>European Institute on Economics and the Environment and KID School of Public Policy</t>
-  </si>
-  <si>
     <t>European Institute on Economics and the Environment and Bocconi University</t>
   </si>
   <si>
@@ -521,24 +476,12 @@
     <t>Air Quality and School Abenteeism: Evidence from New York City</t>
   </si>
   <si>
-    <t>Spring 2022</t>
-  </si>
-  <si>
     <t>Air Pollution and Domestic Violence</t>
   </si>
   <si>
-    <t>Ireri Hernandez</t>
-  </si>
-  <si>
     <t>The Effect of Changing Marginal Cost to Physical Order Dispatch in the Power Sector</t>
   </si>
   <si>
-    <t>Raul Gutierrez and Juan Rosellón</t>
-  </si>
-  <si>
-    <t>European Institute on Economics and the Environment, University of Chicago, and CIDE Mexico</t>
-  </si>
-  <si>
     <t>WorkingVersion</t>
   </si>
   <si>
@@ -554,24 +497,6 @@
     <t>U.S. Net-Zero Technology Pathways of Carbon Management</t>
   </si>
   <si>
-    <t>John Bistline, Carol Lenox, Nadja Victor, Gokul Iyer, Mathew Binsted, Leonard Göke, and others</t>
-  </si>
-  <si>
-    <t>Studying EMF37 high-electrification scenarios in the European Context.</t>
-  </si>
-  <si>
-    <t>Johannes Emmerling, Leonard Göke, Karlo Hainsch</t>
-  </si>
-  <si>
-    <t>European Institute on Economics and the Environment, TU Berlin</t>
-  </si>
-  <si>
-    <t>European Instiute on Economics and the Environment, TU Berlin, USDAM ONNL, UMD, NETL, EPA, MIT, NREL</t>
-  </si>
-  <si>
-    <t>Underlying Beliefs across the Atlantic Looking at heterogenous assumptions in North American and European energy models</t>
-  </si>
-  <si>
     <t>An Econometric Analysis of Environmental Phenomena</t>
   </si>
   <si>
@@ -606,9 +531,6 @@
   </si>
   <si>
     <t>Semester</t>
-  </si>
-  <si>
-    <t>Winter</t>
   </si>
   <si>
     <t>Summer</t>
@@ -641,8 +563,249 @@
  </t>
   </si>
   <si>
-    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Research and publication of scientific articles in the realm of energy and environmental economics. &lt;br&gt;&lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Research projects on the effects of air pollution and air pollution control policies on productivity, health, and wellbeing.</t>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Juan Rosellon  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Sauleh Sidiqui  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Max Brown  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Avraam Charalampos  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  Anahi Molar  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Baltazar Solano &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC and DIW Berlin &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; CIDE &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; American University &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  National Renewable Energy Laboratory &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Munich Insititute of Technology &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; New York University &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  University College London &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Affiliations</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento  &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Sara Giarola&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  Kathleen Vaillancourt&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  Max Brown&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  Anahi Molar&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  Ivan Garcia Kerdan&lt;br&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; University College London  &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &amp; DIW Berlin  &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; ESMIA Consultants &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;  National Renewable Energy Laboratory &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Munich Insititute of Technology &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University College London &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Julio Fournier&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento  &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;Thorstan Burandt&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Konstantin Löffler&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Pao-yu Oei&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt;  RFF-CMCC</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC</t>
+  </si>
+  <si>
+    <t>Journal of Environmental Economics and Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; KDI School of Public Management &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t>R&amp;R</t>
+  </si>
+  <si>
+    <t>Economics of Energy and Environmental Policy</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Illinois &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; CIDE Mexico</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Bergen &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; German Ministry for Economic Affairs</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Bergen &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; German Ministry for Economic Affairs</t>
+  </si>
+  <si>
+    <t>Environmental and Resource Economics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Bocconi University &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Yeong-Jae Kim</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Nicole Wägner &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Aleksandar Zaklan &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Julia Rechlitz &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Nicole Wägner &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Aleksandar Zaklan &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Raul Gutierrez-Meave &lt;br&gt;&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Juan Rosellon &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Adam Nowakowski &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>Winter  (upcoming)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Berlin Institute of Technology &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Berlin Institute of Technology &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Flensburg &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Bergen &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Ireri Hernandez </t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Soheil Shayegh &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Evan Altman  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Chiara Serra  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Simone Ferro  &lt;br&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Nicole Wägner &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Adrian Santoja </t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Severin Reissl &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Johanness Emmerling  &lt;br&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Several Institutions &lt;br&gt; </t>
+  </si>
+  <si>
+    <t>Comparing Net Zero pathways across the Atlantic:  A model inter-comparison exercise between the Energy Modeling Forum 37 and the European Climate and Energy Modeling Forum</t>
+  </si>
+  <si>
+    <t>The Equity Impacts of Net Zero scenarios un the United States</t>
+  </si>
+  <si>
+    <t>The air pollution consequences of Net Zero scenarios in the United States</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Jae Edmons&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;John Bistline&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; John Bistline  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Chikara Onda&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Johaness Emmerling&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Robert Pizsiker&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Dan Loughlin  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Johaness Emmerling&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
+  </si>
+  <si>
+    <t>The Effect of Air purifiers on children' health, attitudes, and performance: Evidence from an RCT in Milan</t>
+  </si>
+  <si>
+    <t>Spring 2024</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Jacopo Bonan &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Francesco Granella  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Stefania Renna  &lt;br&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Politecnico di Milano &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Politecnico di Milano </t>
+  </si>
+  <si>
+    <t>ICEE World Congress</t>
+  </si>
+  <si>
+    <t>Cagliari</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Emory University &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Bocconi University &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Milan &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Publication of scientific articles on energy and environmental economics. &lt;br&gt;&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Research on the effects of air pollution and air pollution control policies on productivity, health, and wellbeing.</t>
+  </si>
+  <si>
+    <t>Summer 2022</t>
+  </si>
+  <si>
+    <t>Winter 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1175,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -1023,16 +1186,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="128" x14ac:dyDescent="0.2">
@@ -1043,16 +1206,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -1063,16 +1226,16 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1086,13 +1249,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1106,13 +1269,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1122,706 +1285,8 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="48.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2021</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2019</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2018</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2022</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C8" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="C1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>2022</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="C2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>2022</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2022</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="C4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2022</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="F6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2021</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="F7" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2020</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="C8" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2020</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:F9" xr:uid="{00000000-0009-0000-0000-000008000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F6">
-      <sortCondition descending="1" ref="A1:A6"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4C3DCE-9179-FF47-845E-F73719ADC20F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="109" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -1853,13 +1318,13 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
@@ -1867,16 +1332,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>7</v>
@@ -1887,16 +1352,16 @@
         <v>2022</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -1904,13 +1369,13 @@
         <v>2022</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -1918,50 +1383,50 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>12</v>
@@ -1972,16 +1437,16 @@
         <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -1989,33 +1454,33 @@
         <v>2019</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -2023,33 +1488,33 @@
         <v>2018</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>12</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -2057,13 +1522,13 @@
         <v>2017</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>12</v>
@@ -2074,45 +1539,64 @@
         <v>2017</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
         <v>78</v>
       </c>
       <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>2017</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>89</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="E4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="E5" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="E6" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="E7" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
-    <hyperlink ref="E8" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-    <hyperlink ref="E9" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
-    <hyperlink ref="E10" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
-    <hyperlink ref="E11" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
-    <hyperlink ref="E12" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
-    <hyperlink ref="E13" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
-    <hyperlink ref="E14" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
-    <hyperlink ref="E15" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
-    <hyperlink ref="E2" r:id="rId14" xr:uid="{78A67955-616F-7E42-B61F-F4B85583B5E0}"/>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="E5" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="E8" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="E11" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="E12" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
+    <hyperlink ref="E13" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
+    <hyperlink ref="E14" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
+    <hyperlink ref="E15" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
+    <hyperlink ref="E16" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
+    <hyperlink ref="E3" r:id="rId14" xr:uid="{78A67955-616F-7E42-B61F-F4B85583B5E0}"/>
+    <hyperlink ref="E2" r:id="rId15" xr:uid="{AFCFE2FC-4800-F44C-B16D-33750E5850A6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D9F129-3957-8D46-A9B7-45930C043918}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
@@ -2124,16 +1608,16 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="C1" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D1" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="E1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -2144,16 +1628,16 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="E2" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>7</v>
@@ -2164,16 +1648,16 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="D3" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>7</v>
@@ -2184,16 +1668,16 @@
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="E4" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
@@ -2204,16 +1688,16 @@
         <v>2018</v>
       </c>
       <c r="B5" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
@@ -2231,7 +1715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2256,19 +1740,19 @@
         <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>96</v>
+        <v>171</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
@@ -2276,22 +1760,25 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="C2" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -2302,71 +1789,74 @@
         <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="D3" t="s">
+        <v>175</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2021</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" t="s">
-        <v>100</v>
+        <v>98</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>146</v>
+        <v>173</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
+        <v>99</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>176</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -2374,51 +1864,51 @@
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" t="s">
-        <v>103</v>
+        <v>101</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="144" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2019</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
-      </c>
-      <c r="D7" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>180</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>147</v>
+        <v>198</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2426,10 +1916,760 @@
     <hyperlink ref="G6" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
     <hyperlink ref="G7" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
     <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
-    <hyperlink ref="G3" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="G2" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="G3" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="G2" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="G4" r:id="rId6" xr:uid="{0E9F22AE-FE52-5943-8334-B9F647A556BE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="65" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.83203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2021</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2019</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2018</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2022</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2020</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2022</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" t="s">
+        <v>190</v>
+      </c>
+      <c r="D9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>2022</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>2023</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C4" t="s">
+        <v>150</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2023</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2021</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2020</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>2020</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" t="s">
+        <v>150</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>2022</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F9" xr:uid="{00000000-0009-0000-0000-000008000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F6">
+      <sortCondition descending="1" ref="A1:A6"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4C3DCE-9179-FF47-845E-F73719ADC20F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="109" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luissarmiento/Dropbox (CMCC)/EIEE/Website/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17E79F29-E5CF-4F4D-89E8-3E85DE70C98A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0185472E-BB52-FD4E-8E67-199A5B6B3B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10514"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luissarmiento/Dropbox (CMCC)/EIEE/Website/mysite/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0185472E-BB52-FD4E-8E67-199A5B6B3B48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B35765-683A-AB4A-B0B6-8D824AE851F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Teaching!$A$1:$A$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">UnderwayResearch!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">UnderwayResearch!$A$1:$F$7</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="218">
   <si>
     <t>Dates</t>
   </si>
@@ -362,9 +362,6 @@
     <t>Journal of Public Economics</t>
   </si>
   <si>
-    <t>Nature Sustainability</t>
-  </si>
-  <si>
     <t>The Unaccounted Consequences of Low Emission Zones: Evidence from Madrid Central</t>
   </si>
   <si>
@@ -377,9 +374,6 @@
     <t>Air Pollution and Court Decisions: Evidence from Ten Million Penal Cases in India</t>
   </si>
   <si>
-    <t>Adam Nowakowski</t>
-  </si>
-  <si>
     <t>The Agent Base Model of Technology Adoption ABM-REN</t>
   </si>
   <si>
@@ -446,9 +440,6 @@
     <t>Institute</t>
   </si>
   <si>
-    <t>European Institute on Economics and the Environment and Bocconi University</t>
-  </si>
-  <si>
     <t>European Institute on Economics and the Environment</t>
   </si>
   <si>
@@ -474,12 +465,6 @@
   </si>
   <si>
     <t>Air Quality and School Abenteeism: Evidence from New York City</t>
-  </si>
-  <si>
-    <t>Air Pollution and Domestic Violence</t>
-  </si>
-  <si>
-    <t>The Effect of Changing Marginal Cost to Physical Order Dispatch in the Power Sector</t>
   </si>
   <si>
     <t>WorkingVersion</t>
@@ -629,9 +614,6 @@
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC</t>
   </si>
   <si>
-    <t>Journal of Environmental Economics and Management</t>
-  </si>
-  <si>
     <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
 &lt;span&gt;&amp;#8226;&lt;/span&gt; KDI School of Public Management &lt;br&gt;
 </t>
@@ -662,11 +644,6 @@
     <t>Environmental and Resource Economics</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Bocconi University &lt;br&gt;
-</t>
-  </si>
-  <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Yeong-Jae Kim</t>
   </si>
@@ -684,10 +661,6 @@
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Raul Gutierrez-Meave &lt;br&gt;&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Juan Rosellon &lt;br&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Adam Nowakowski &lt;br&gt;</t>
   </si>
   <si>
     <t>Winter  (upcoming)</t>
@@ -705,10 +678,6 @@
 &lt;span&gt;&amp;#8226;&lt;/span&gt; DIW Berlin </t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Ireri Hernandez </t>
-  </si>
-  <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Soheil Shayegh &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Evan Altman  &lt;br&gt;
@@ -735,9 +704,6 @@
     <t>The Equity Impacts of Net Zero scenarios un the United States</t>
   </si>
   <si>
-    <t>The air pollution consequences of Net Zero scenarios in the United States</t>
-  </si>
-  <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Jae Edmons&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt;John Bistline&lt;br&gt;
@@ -753,12 +719,6 @@
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Johaness Emmerling&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Robert Pizsiker&lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Dan Loughlin  &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Johaness Emmerling&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
   </si>
   <si>
@@ -800,12 +760,35 @@
     <t>Summer 2022</t>
   </si>
   <si>
-    <t>Winter 2023</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 &lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Adam Nowakowski  &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t>Policy Reversals in Transitional Markets: The Effect of Changing Marginal Cost to Physical Order Dispatch in the Power Sector</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://www.springer.com/journal/10640'&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC  &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Bocconi University &lt;br&gt;
+</t>
+  </si>
+  <si>
+    <t>Environment International</t>
+  </si>
+  <si>
+    <t>Journal of the European Economic Association</t>
   </si>
 </sst>
 </file>
@@ -1175,7 +1158,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="160" x14ac:dyDescent="0.2">
@@ -1186,16 +1169,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="128" x14ac:dyDescent="0.2">
@@ -1206,16 +1189,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -1226,16 +1209,16 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -1249,13 +1232,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -1269,13 +1252,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1318,13 +1301,13 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
@@ -1335,13 +1318,13 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>7</v>
@@ -1608,16 +1591,16 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -1628,16 +1611,16 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>7</v>
@@ -1648,16 +1631,16 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>7</v>
@@ -1668,16 +1651,16 @@
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C4" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D4" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
@@ -1688,16 +1671,16 @@
         <v>2018</v>
       </c>
       <c r="B5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C5" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D5" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E5" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
@@ -1717,7 +1700,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="43.6640625" customWidth="1"/>
@@ -1740,114 +1723,114 @@
         <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" t="s">
-        <v>175</v>
+        <v>184</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>128</v>
+        <v>214</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>181</v>
+        <v>215</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="96" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>175</v>
+        <v>180</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>129</v>
+        <v>213</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="176" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>172</v>
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
+        <v>170</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>176</v>
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>170</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>177</v>
@@ -1856,69 +1839,124 @@
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="176" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="192" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H7" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>2021</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" t="s">
         <v>101</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="D8" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="144" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="H8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>2019</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B9" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="D9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="H7" t="s">
-        <v>139</v>
+      <c r="H9" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G6" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="G7" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="G5" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="G3" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="G2" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
-    <hyperlink ref="G4" r:id="rId6" xr:uid="{0E9F22AE-FE52-5943-8334-B9F647A556BE}"/>
+    <hyperlink ref="G8" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="G9" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="G7" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="G4" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="G6" r:id="rId6" xr:uid="{0E9F22AE-FE52-5943-8334-B9F647A556BE}"/>
+    <hyperlink ref="G2" r:id="rId7" xr:uid="{C49C3694-DD44-6F4D-AB60-4C8AF8F149C4}"/>
+    <hyperlink ref="B3" r:id="rId8" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{5029F8FF-F0C2-764C-A12A-A637FE8680B9}"/>
+    <hyperlink ref="G3" r:id="rId9" xr:uid="{4C50AA69-EC7E-5E42-B35C-61ECE2CDF538}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1926,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="65" style="1" bestFit="1" customWidth="1"/>
@@ -1951,16 +1989,16 @@
         <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -1971,22 +2009,22 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="D2" t="s">
         <v>104</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -2000,19 +2038,19 @@
         <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="80" x14ac:dyDescent="0.2">
@@ -2023,22 +2061,22 @@
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="D4" t="s">
         <v>104</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
@@ -2046,134 +2084,56 @@
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" t="s">
         <v>108</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>112</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2021</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2022</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D9" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
@@ -2191,16 +2151,16 @@
         <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="F1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="80" x14ac:dyDescent="0.2">
@@ -2208,19 +2168,19 @@
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -2228,19 +2188,19 @@
         <v>2023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
@@ -2248,145 +2208,105 @@
         <v>2023</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>2021</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C5" t="s">
         <v>209</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>2020</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>2023</v>
-      </c>
-      <c r="B5" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C5" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2021</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C6" t="s">
-        <v>220</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="F6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A7">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C7" t="s">
         <v>145</v>
       </c>
-      <c r="C7" t="s">
-        <v>221</v>
-      </c>
       <c r="D7" s="1" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F7" t="s">
-        <v>138</v>
+        <v>210</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="80" x14ac:dyDescent="0.2">
       <c r="A8">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="C8" t="s">
-        <v>142</v>
+        <v>202</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="F8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>2020</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="C9" t="s">
-        <v>150</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="80" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>2022</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="C10" t="s">
-        <v>213</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>138</v>
+        <v>204</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F9" xr:uid="{00000000-0009-0000-0000-000008000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F6">
-      <sortCondition descending="1" ref="A1:A6"/>
+  <autoFilter ref="A1:F7" xr:uid="{00000000-0009-0000-0000-000008000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F5">
+      <sortCondition descending="1" ref="A1:A5"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2423,7 +2343,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -2437,13 +2357,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -2463,7 +2383,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -2483,7 +2403,7 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10719"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luissarmiento/Dropbox (CMCC)/EIEE/Website/mysite/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sarmiento\Dropbox (CMCC)\EIEE\Website\mysite\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B35765-683A-AB4A-B0B6-8D824AE851F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3940" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3945" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -356,9 +355,6 @@
     <t>Under Review</t>
   </si>
   <si>
-    <t>Effectiveness, Spillovers, and Well-Being Effects of Driving Restriction Policies</t>
-  </si>
-  <si>
     <t>Journal of Public Economics</t>
   </si>
   <si>
@@ -619,20 +615,12 @@
 </t>
   </si>
   <si>
-    <t>R&amp;R</t>
-  </si>
-  <si>
     <t>Economics of Energy and Environmental Policy</t>
   </si>
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
 &lt;span&gt;&amp;#8226;&lt;/span&gt; University of Illinois &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; CIDE Mexico</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
-&lt;span&gt;&amp;#8226;&lt;/span&gt; University of Bergen &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; German Ministry for Economic Affairs</t>
   </si>
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
@@ -646,11 +634,6 @@
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Yeong-Jae Kim</t>
-  </si>
-  <si>
-    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Nicole Wägner &lt;br&gt;
-&lt;span&gt;&amp;#8226;&lt;/span&gt; Aleksandar Zaklan &lt;br&gt;</t>
   </si>
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
@@ -790,11 +773,27 @@
   <si>
     <t>Journal of the European Economic Association</t>
   </si>
+  <si>
+    <t>The Air Quality and Well-Being Effects of Low Emission Zones</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento&lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Nicole Wägner  &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Aleksandar Zaklan  &lt;br&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://media.rff.org/documents/EIEE_WP_21-13.pdf'&gt;</t>
+  </si>
+  <si>
+    <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
+&lt;span&gt;&amp;#8226;&lt;/span&gt; Norwegian School of Economics &lt;br&gt;
+&lt;span&gt;&amp;#8226;&lt;/span&gt; German Ministry for Economic Affairs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1128,20 +1127,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.1640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="47.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="63.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="47.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="63.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.7109375" style="2" customWidth="1"/>
     <col min="6" max="6" width="84" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.1640625" style="2"/>
+    <col min="7" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1158,10 +1157,10 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="160" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -1169,19 +1168,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="128" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1189,19 +1188,19 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1209,19 +1208,19 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -1232,16 +1231,16 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1252,13 +1251,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -1268,18 +1267,18 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="91" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="54.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>93</v>
       </c>
@@ -1296,41 +1295,41 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2022</v>
       </c>
@@ -1347,7 +1346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2022</v>
       </c>
@@ -1364,7 +1363,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2022</v>
       </c>
@@ -1381,7 +1380,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -1398,7 +1397,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2020</v>
       </c>
@@ -1415,7 +1414,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2019</v>
       </c>
@@ -1432,7 +1431,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>2019</v>
       </c>
@@ -1449,7 +1448,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2019</v>
       </c>
@@ -1466,7 +1465,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>2018</v>
       </c>
@@ -1483,7 +1482,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>2018</v>
       </c>
@@ -1500,7 +1499,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>2017</v>
       </c>
@@ -1517,7 +1516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2017</v>
       </c>
@@ -1534,7 +1533,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2017</v>
       </c>
@@ -1553,166 +1552,166 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="E5" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="E8" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
-    <hyperlink ref="E9" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-    <hyperlink ref="E10" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
-    <hyperlink ref="E11" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
-    <hyperlink ref="E12" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
-    <hyperlink ref="E13" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
-    <hyperlink ref="E14" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
-    <hyperlink ref="E15" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
-    <hyperlink ref="E16" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
-    <hyperlink ref="E3" r:id="rId14" xr:uid="{78A67955-616F-7E42-B61F-F4B85583B5E0}"/>
-    <hyperlink ref="E2" r:id="rId15" xr:uid="{AFCFE2FC-4800-F44C-B16D-33750E5850A6}"/>
+    <hyperlink ref="E4" r:id="rId1"/>
+    <hyperlink ref="E5" r:id="rId2"/>
+    <hyperlink ref="E6" r:id="rId3"/>
+    <hyperlink ref="E7" r:id="rId4"/>
+    <hyperlink ref="E8" r:id="rId5"/>
+    <hyperlink ref="E9" r:id="rId6"/>
+    <hyperlink ref="E10" r:id="rId7"/>
+    <hyperlink ref="E11" r:id="rId8"/>
+    <hyperlink ref="E12" r:id="rId9"/>
+    <hyperlink ref="E13" r:id="rId10"/>
+    <hyperlink ref="E14" r:id="rId11"/>
+    <hyperlink ref="E15" r:id="rId12"/>
+    <hyperlink ref="E16" r:id="rId13"/>
+    <hyperlink ref="E3" r:id="rId14"/>
+    <hyperlink ref="E2" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40D9F129-3957-8D46-A9B7-45930C043918}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E2" t="s">
         <v>152</v>
-      </c>
-      <c r="E2" t="s">
-        <v>153</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" t="s">
         <v>152</v>
-      </c>
-      <c r="E3" t="s">
-        <v>153</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C4" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" t="s">
         <v>148</v>
       </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
       <c r="E4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2018</v>
       </c>
       <c r="B5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D5" t="s">
         <v>148</v>
       </c>
-      <c r="D5" t="s">
-        <v>149</v>
-      </c>
       <c r="E5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A5" xr:uid="{40D9F129-3957-8D46-A9B7-45930C043918}"/>
+  <autoFilter ref="A1:A5"/>
   <hyperlinks>
-    <hyperlink ref="F5" r:id="rId1" xr:uid="{98A7B022-2468-3A42-9840-4CD5A7546650}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{6AC88186-953E-7C49-9BC5-459F7E0D56E9}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{D3EAC5C6-A852-8646-8BCA-DCF0BFE92212}"/>
-    <hyperlink ref="F2" r:id="rId4" xr:uid="{268C2E99-BF62-2746-8773-5F81D79F7290}"/>
+    <hyperlink ref="F5" r:id="rId1"/>
+    <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F2" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="44.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="45.5" customWidth="1"/>
-    <col min="5" max="5" width="27.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="40.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="51.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.7109375" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="38.28515625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="40.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="51.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>93</v>
       </c>
@@ -1723,91 +1722,91 @@
         <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2023</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>105</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="96" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="48" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" t="s">
-        <v>170</v>
+        <v>178</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
@@ -1816,59 +1815,59 @@
         <v>135</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="176" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>167</v>
+        <v>97</v>
+      </c>
+      <c r="D6" t="s">
+        <v>169</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="192" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2021</v>
       </c>
@@ -1876,106 +1875,133 @@
         <v>122</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="195" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2021</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="H8" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="144" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="135" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2019</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H10" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G8" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
-    <hyperlink ref="G9" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
-    <hyperlink ref="G7" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
-    <hyperlink ref="G5" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
-    <hyperlink ref="G4" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
-    <hyperlink ref="G6" r:id="rId6" xr:uid="{0E9F22AE-FE52-5943-8334-B9F647A556BE}"/>
-    <hyperlink ref="G2" r:id="rId7" xr:uid="{C49C3694-DD44-6F4D-AB60-4C8AF8F149C4}"/>
-    <hyperlink ref="B3" r:id="rId8" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/" xr:uid="{5029F8FF-F0C2-764C-A12A-A637FE8680B9}"/>
-    <hyperlink ref="G3" r:id="rId9" xr:uid="{4C50AA69-EC7E-5E42-B35C-61ECE2CDF538}"/>
+    <hyperlink ref="G9" r:id="rId1"/>
+    <hyperlink ref="G10" r:id="rId2"/>
+    <hyperlink ref="G8" r:id="rId3"/>
+    <hyperlink ref="G6" r:id="rId4"/>
+    <hyperlink ref="G5" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G3" r:id="rId7"/>
+    <hyperlink ref="B4" r:id="rId8" display="https://www.rff.org/publications/working-papers/effect-of-changing-marginal-cost-to-physical-order-dispatch-in-the-power-sector/"/>
+    <hyperlink ref="G4" r:id="rId9"/>
+    <hyperlink ref="G2" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="40.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="40" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -1989,19 +2015,19 @@
         <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2021</v>
       </c>
@@ -2009,120 +2035,94 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D2" t="s">
         <v>104</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2021</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="80" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>2018</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>216</v>
-      </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>187</v>
+        <v>108</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="64" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
         <v>107</v>
       </c>
-      <c r="D5" t="s">
-        <v>108</v>
-      </c>
       <c r="E5" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>135</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>2020</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2132,18 +2132,18 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>102</v>
       </c>
@@ -2151,161 +2151,161 @@
         <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>2022</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="48" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2021</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="150" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2020</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="64" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2020</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="80" x14ac:dyDescent="0.2">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2022</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C8" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7" xr:uid="{00000000-0009-0000-0000-000008000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F5">
+  <autoFilter ref="A1:F7">
+    <sortState ref="A2:F5">
       <sortCondition descending="1" ref="A1:A5"/>
     </sortState>
   </autoFilter>
@@ -2314,19 +2314,19 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="74.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="51.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="51.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2343,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -2357,16 +2357,16 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -2383,10 +2383,10 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>28</v>
       </c>
@@ -2403,7 +2403,7 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2412,24 +2412,24 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4C3DCE-9179-FF47-845E-F73719ADC20F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="109" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -2475,15 +2475,15 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
@@ -2499,7 +2499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -2507,7 +2507,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>47</v>
       </c>
@@ -2523,7 +2523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>48</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>49</v>
       </c>
@@ -2545,11 +2545,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>42</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>50</v>
       </c>
@@ -2565,7 +2565,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>51</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>53</v>
       </c>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="3945" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="1"/>
+    <workbookView xWindow="3945" yWindow="0" windowWidth="27780" windowHeight="18000" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Occupation" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Teaching!$A$1:$A$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">UnderwayResearch!$A$1:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">UnderwayResearch!$A$1:$F$5</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="214">
   <si>
     <t>Dates</t>
   </si>
@@ -361,21 +361,12 @@
     <t>The Unaccounted Consequences of Low Emission Zones: Evidence from Madrid Central</t>
   </si>
   <si>
-    <t>Working Paper</t>
-  </si>
-  <si>
-    <t>Adrian Santoja and Nicole Wägner</t>
-  </si>
-  <si>
     <t>Air Pollution and Court Decisions: Evidence from Ten Million Penal Cases in India</t>
   </si>
   <si>
     <t>The Agent Base Model of Technology Adoption ABM-REN</t>
   </si>
   <si>
-    <t>Severin Reissl and Johanness Emmerling</t>
-  </si>
-  <si>
     <t>link</t>
   </si>
   <si>
@@ -436,12 +427,6 @@
     <t>Institute</t>
   </si>
   <si>
-    <t>European Institute on Economics and the Environment</t>
-  </si>
-  <si>
-    <t>European Institute on Economics and the Environment, German_x000D_ Institute of Economic Research, and Leibniz Institute for Economic Research</t>
-  </si>
-  <si>
     <t>econometrics</t>
   </si>
   <si>
@@ -452,9 +437,6 @@
   </si>
   <si>
     <t>Expected</t>
-  </si>
-  <si>
-    <t>Winter 2022</t>
   </si>
   <si>
     <t>Spring 2023</t>
@@ -684,9 +666,6 @@
     <t>Comparing Net Zero pathways across the Atlantic:  A model inter-comparison exercise between the Energy Modeling Forum 37 and the European Climate and Energy Modeling Forum</t>
   </si>
   <si>
-    <t>The Equity Impacts of Net Zero scenarios un the United States</t>
-  </si>
-  <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Luis Sarmiento &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Jae Edmons&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt;John Bistline&lt;br&gt;
@@ -703,12 +682,6 @@
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Johaness Emmerling&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Robert Pizsiker&lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt;….. and others&lt;br&gt;</t>
-  </si>
-  <si>
-    <t>The Effect of Air purifiers on children' health, attitudes, and performance: Evidence from an RCT in Milan</t>
-  </si>
-  <si>
-    <t>Spring 2024</t>
   </si>
   <si>
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; Jacopo Bonan &lt;br&gt;
@@ -740,9 +713,6 @@
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Research on the effects of air pollution and air pollution control policies on productivity, health, and wellbeing.</t>
   </si>
   <si>
-    <t>Summer 2022</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 &lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
 </t>
@@ -788,6 +758,24 @@
     <t>&lt;span&gt;&amp;#8226;&lt;/span&gt; RFF-CMCC &lt;br&gt; 
 &lt;span&gt;&amp;#8226;&lt;/span&gt; Norwegian School of Economics &lt;br&gt;
 &lt;span&gt;&amp;#8226;&lt;/span&gt; German Ministry for Economic Affairs</t>
+  </si>
+  <si>
+    <t>Energy and Climate Change</t>
+  </si>
+  <si>
+    <t>Equity Implications of Net-Zero Emissions: A Multi-Model Analysis of Distributional Effects Across Income Classes</t>
+  </si>
+  <si>
+    <t>Journal of Political Economy: Microeconomics</t>
+  </si>
+  <si>
+    <t>Indoor air quality and student welfare: The Effect of Indoor Air Purifiers in Schools</t>
+  </si>
+  <si>
+    <t>Summer 2023</t>
+  </si>
+  <si>
+    <t>Winter 2023</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1145,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="195" x14ac:dyDescent="0.25">
@@ -1168,16 +1156,16 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="150" x14ac:dyDescent="0.25">
@@ -1188,16 +1176,16 @@
         <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>7</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
@@ -1208,16 +1196,16 @@
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1231,13 +1219,13 @@
         <v>14</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1251,13 +1239,13 @@
         <v>17</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1300,13 +1288,13 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
         <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>7</v>
@@ -1317,13 +1305,13 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="C3" t="s">
         <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>7</v>
@@ -1590,16 +1578,16 @@
         <v>93</v>
       </c>
       <c r="B1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -1610,16 +1598,16 @@
         <v>2023</v>
       </c>
       <c r="B2" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E2" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>7</v>
@@ -1630,16 +1618,16 @@
         <v>2023</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D3" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E3" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>7</v>
@@ -1650,16 +1638,16 @@
         <v>2019</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>12</v>
@@ -1670,16 +1658,16 @@
         <v>2018</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>12</v>
@@ -1722,19 +1710,19 @@
         <v>95</v>
       </c>
       <c r="D1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
@@ -1742,25 +1730,25 @@
         <v>2023</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C2" t="s">
         <v>105</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
@@ -1768,80 +1756,80 @@
         <v>2023</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="105" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2023</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C4" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G4" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2022</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C5" t="s">
         <v>96</v>
       </c>
       <c r="D5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>175</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2021</v>
       </c>
@@ -1852,19 +1840,19 @@
         <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="195" x14ac:dyDescent="0.25">
@@ -1872,25 +1860,25 @@
         <v>2021</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
         <v>98</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="G7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="195" x14ac:dyDescent="0.25">
@@ -1898,51 +1886,51 @@
         <v>2021</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" t="s">
         <v>99</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2021</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C9" t="s">
         <v>101</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="135" x14ac:dyDescent="0.25">
@@ -1950,25 +1938,25 @@
         <v>2019</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -1990,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="65" style="1" bestFit="1" customWidth="1"/>
@@ -2015,16 +2003,16 @@
         <v>103</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
@@ -2035,22 +2023,22 @@
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D2" t="s">
         <v>104</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
@@ -2061,68 +2049,100 @@
         <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="D3" t="s">
         <v>104</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="60" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>106</v>
+        <v>186</v>
+      </c>
+      <c r="C4" t="s">
+        <v>208</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>108</v>
+        <v>189</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>209</v>
+      </c>
+      <c r="C5" t="s">
+        <v>208</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2023</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2133,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
@@ -2151,160 +2171,100 @@
         <v>94</v>
       </c>
       <c r="C1" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2021</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2020</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2020</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2023</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>2023</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="C4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2021</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C5" t="s">
-        <v>205</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="150" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>2020</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>2020</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C7" t="s">
-        <v>144</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="120" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>2022</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C8" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>134</v>
+      <c r="F5" s="1" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F7">
+  <autoFilter ref="A1:F5">
     <sortState ref="A2:F5">
       <sortCondition descending="1" ref="A1:A5"/>
     </sortState>
@@ -2343,7 +2303,7 @@
         <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2357,13 +2317,13 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,7 +2343,7 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,7 +2363,7 @@
         <v>18</v>
       </c>
       <c r="F4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
